--- a/docs/design-vi/ACSMS-SCR-016/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者Excelデータ取込画面_v1.0.xlsx
+++ b/docs/design-vi/ACSMS-SCR-016/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者Excelデータ取込画面_v1.0.xlsx
@@ -1200,7 +1200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH2"/>
+  <dimension ref="A1:AH3"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="3.33" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1365,20 +1365,80 @@
       <c r="AG2" s="10" t="n"/>
       <c r="AH2" s="11" t="n"/>
     </row>
+    <row r="3" ht="22.5" customHeight="1">
+      <c r="A3" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="19" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="11" t="n"/>
+      <c r="I3" s="19" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="n"/>
+      <c r="K3" s="10" t="n"/>
+      <c r="L3" s="10" t="n"/>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="11" t="n"/>
+      <c r="O3" s="20" t="inlineStr">
+        <is>
+          <t>Đồng bộ với bản tiếng Nhật: ①sửa số cột template từ 49 cột → 50 cột (12 chỗ). Bản này dừng ở 2026-06-05 nên chưa phản ánh 49→48 (bỏ loại đăng ký khỏi cột), 48→46 (chuyển ngày áp dụng・ngày ngừng sang ô nhập màn hình) và 46→50 (#56405 thêm 4 mục phụ thuộc của phân loại tầng lớp người đọc). ②bổ sung 6 ca kiểm thử 052〜057 và tạo カテゴリ10 (tổng 51 → 57)</t>
+        </is>
+      </c>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="10" t="n"/>
+      <c r="S3" s="10" t="n"/>
+      <c r="T3" s="10" t="n"/>
+      <c r="U3" s="10" t="n"/>
+      <c r="V3" s="11" t="n"/>
+      <c r="W3" s="19" t="inlineStr"/>
+      <c r="X3" s="10" t="n"/>
+      <c r="Y3" s="10" t="n"/>
+      <c r="Z3" s="10" t="n"/>
+      <c r="AA3" s="10" t="n"/>
+      <c r="AB3" s="11" t="n"/>
+      <c r="AC3" s="19" t="inlineStr"/>
+      <c r="AD3" s="10" t="n"/>
+      <c r="AE3" s="10" t="n"/>
+      <c r="AF3" s="10" t="n"/>
+      <c r="AG3" s="10" t="n"/>
+      <c r="AH3" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="18">
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="AC2:AH2"/>
     <mergeCell ref="AC1:AH1"/>
+    <mergeCell ref="O3:V3"/>
     <mergeCell ref="I2:N2"/>
     <mergeCell ref="O2:V2"/>
     <mergeCell ref="W1:AB1"/>
     <mergeCell ref="F1:H1"/>
+    <mergeCell ref="W3:AB3"/>
     <mergeCell ref="O1:V1"/>
     <mergeCell ref="I1:N1"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="I3:N3"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="W2:AB2"/>
+    <mergeCell ref="AC3:AH3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6302,7 +6362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ71"/>
+  <dimension ref="A1:BQ78"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -8930,7 +8990,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Panel cột import được hiển thị, checkbox cho cả 49 cột được hiển thị
+            <t xml:space="preserve">Panel cột import được hiển thị, checkbox cho cả 50 cột được hiển thị
 </t>
           </r>
           <r>
@@ -8981,7 +9041,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Thứ tự cột khớp với file template (cố định 49 cột)
+            <t xml:space="preserve">・Thứ tự cột khớp với file template (cố định 50 cột)
 </t>
           </r>
           <r>
@@ -10606,7 +10666,7 @@
         <is>
           <t>・role: JA_HONTEN
 ・Đã login + đã xác thực MFA
-・File test: `.xlsx` chứa 3 dòng độc giả, sheet name "購読者", 49 cột header</t>
+・File test: `.xlsx` chứa 3 dòng độc giả, sheet name "購読者", 50 cột header</t>
         </is>
       </c>
       <c r="K31" s="10" t="n"/>
@@ -10992,7 +11052,7 @@
       <c r="BP32" s="10" t="n"/>
       <c r="BQ32" s="11" t="n"/>
     </row>
-    <row r="33" ht="288" customHeight="1">
+    <row r="33" ht="320" customHeight="1">
       <c r="A33" s="44" t="n">
         <v>18</v>
       </c>
@@ -11041,7 +11101,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Xác nhận preview ban đầu hiển thị đủ 49 cột
+            <t xml:space="preserve">Xác nhận preview ban đầu hiển thị đủ 50 cột
 </t>
           </r>
           <r>
@@ -11101,7 +11161,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Preview hiển thị header 49 cột và 3 dòng data
+            <t xml:space="preserve">Preview hiển thị header 50 cột và 3 dòng data
 </t>
           </r>
           <r>
@@ -11135,7 +11195,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">3 cột bị bỏ tick không hiển thị trên preview, chỉ hiển thị header và data của 46 cột
+            <t xml:space="preserve">3 cột bị bỏ tick không hiển thị trên preview, chỉ hiển thị header và data của các cột còn lại (trong tổng 50 cột, trừ đi các cột bị bỏ tick)
 </t>
           </r>
           <r>
@@ -12652,7 +12712,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Sheet name là "購読者", dòng 1 chứa 49 cột header
+            <t xml:space="preserve">Sheet name là "購読者", dòng 1 chứa 50 cột header
 </t>
           </r>
           <r>
@@ -12669,7 +12729,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>・Thứ tự cột theo `screen-design.md §3.1` và `api.md §テンプレートファイル仕様` (cố định 49 cột)</t>
+            <t>・Thứ tự cột theo `screen-design.md §3.1` và `api.md §テンプレートファイル仕様` (cố định 50 cột)</t>
           </r>
         </is>
       </c>
@@ -12736,7 +12796,7 @@
       <c r="D42" s="11" t="n"/>
       <c r="E42" s="46" t="inlineStr">
         <is>
-          <t>Template — kiểm tra thứ tự · số lượng 49 cột header</t>
+          <t>Template — kiểm tra thứ tự · số lượng 50 cột header</t>
         </is>
       </c>
       <c r="F42" s="10" t="n"/>
@@ -12789,7 +12849,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Kiểm tra chuỗi header và số lượng của 49 cột</t>
+            <t>Kiểm tra chuỗi header và số lượng của 50 cột</t>
           </r>
         </is>
       </c>
@@ -12815,7 +12875,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Trên sheet "購読者", dòng 1 hiển thị 49 cột header
+            <t xml:space="preserve">Trên sheet "購読者", dòng 1 hiển thị 50 cột header
 </t>
           </r>
           <r>
@@ -12832,7 +12892,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Các header xếp theo thứ tự định nghĩa của `screen-design.md §画面項目定義` và `api.md §テンプレートファイル仕様`, số cột đúng bằng 49 cột
+            <t xml:space="preserve">Các header xếp theo thứ tự định nghĩa của `screen-design.md §画面項目定義` và `api.md §テンプレートファイル仕様`, số cột đúng bằng 50 cột
 </t>
           </r>
           <r>
@@ -13283,7 +13343,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Trả về HTTP 200, response là `import_mode: "NEW"`, `created_count: 3`, hiển thị toast `正常に取り込みました。` (ACSMS-MSG-016-004), số bản ghi import được hiển thị qua toast
+            <t xml:space="preserve">Trả về HTTP 200, response là `import_mode: "NEW"`, `created_count: 3`, hiển thị toast `取り込みました。` (ACSMS-MSG-016-004), số bản ghi import được hiển thị qua toast
 </t>
           </r>
           <r>
@@ -14867,7 +14927,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Trả về HTTP 200, `import_mode: "UPDATE_ALL"`, `updated_count: 1`, hiển thị toast `正常に取り込みました。` (ACSMS-MSG-016-004)
+            <t xml:space="preserve">Trả về HTTP 200, `import_mode: "UPDATE_ALL"`, `updated_count: 1`, hiển thị toast `取り込みました。` (ACSMS-MSG-016-004)
 </t>
           </r>
           <r>
@@ -15455,7 +15515,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Trả về HTTP 200, `updated_count: 1`, hiển thị toast `正常に取り込みました。` (ACSMS-MSG-016-004)
+            <t xml:space="preserve">Trả về HTTP 200, `updated_count: 1`, hiển thị toast `取り込みました。` (ACSMS-MSG-016-004)
 </t>
           </r>
           <r>
@@ -15778,7 +15838,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Trả về HTTP 200, `import_mode: "UPDATE_PARTIAL"`, `updated_count: 1`, hiển thị toast `正常に取り込みました。` (ACSMS-MSG-016-004)
+            <t xml:space="preserve">Trả về HTTP 200, `import_mode: "UPDATE_PARTIAL"`, `updated_count: 1`, hiển thị toast `取り込みました。` (ACSMS-MSG-016-004)
 </t>
           </r>
           <r>
@@ -16213,7 +16273,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Trả về HTTP 200, `updated_count: 1`, hiển thị toast `正常に取り込みました。` (ACSMS-MSG-016-004)
+            <t xml:space="preserve">Trả về HTTP 200, `updated_count: 1`, hiển thị toast `取り込みました。` (ACSMS-MSG-016-004)
 </t>
           </r>
           <r>
@@ -18139,8 +18199,627 @@
       <c r="BP71" s="10" t="n"/>
       <c r="BQ71" s="11" t="n"/>
     </row>
+    <row r="72" ht="22.5" customHeight="1">
+      <c r="A72" s="32" t="inlineStr">
+        <is>
+          <t>Logic nghiệp vụ — Ngày áp dụng／Ngừng hàng loạt・Mở rộng cột nhập (Function — Dates / Bulk-stop / Columns)</t>
+        </is>
+      </c>
+      <c r="B72" s="10" t="n"/>
+      <c r="C72" s="10" t="n"/>
+      <c r="D72" s="10" t="n"/>
+      <c r="E72" s="10" t="n"/>
+      <c r="F72" s="10" t="n"/>
+      <c r="G72" s="10" t="n"/>
+      <c r="H72" s="10" t="n"/>
+      <c r="I72" s="10" t="n"/>
+      <c r="J72" s="10" t="n"/>
+      <c r="K72" s="10" t="n"/>
+      <c r="L72" s="10" t="n"/>
+      <c r="M72" s="10" t="n"/>
+      <c r="N72" s="10" t="n"/>
+      <c r="O72" s="10" t="n"/>
+      <c r="P72" s="10" t="n"/>
+      <c r="Q72" s="10" t="n"/>
+      <c r="R72" s="10" t="n"/>
+      <c r="S72" s="10" t="n"/>
+      <c r="T72" s="10" t="n"/>
+      <c r="U72" s="10" t="n"/>
+      <c r="V72" s="10" t="n"/>
+      <c r="W72" s="10" t="n"/>
+      <c r="X72" s="10" t="n"/>
+      <c r="Y72" s="10" t="n"/>
+      <c r="Z72" s="10" t="n"/>
+      <c r="AA72" s="10" t="n"/>
+      <c r="AB72" s="10" t="n"/>
+      <c r="AC72" s="10" t="n"/>
+      <c r="AD72" s="10" t="n"/>
+      <c r="AE72" s="10" t="n"/>
+      <c r="AF72" s="10" t="n"/>
+      <c r="AG72" s="10" t="n"/>
+      <c r="AH72" s="10" t="n"/>
+      <c r="AI72" s="10" t="n"/>
+      <c r="AJ72" s="10" t="n"/>
+      <c r="AK72" s="10" t="n"/>
+      <c r="AL72" s="10" t="n"/>
+      <c r="AM72" s="10" t="n"/>
+      <c r="AN72" s="10" t="n"/>
+      <c r="AO72" s="10" t="n"/>
+      <c r="AP72" s="10" t="n"/>
+      <c r="AQ72" s="10" t="n"/>
+      <c r="AR72" s="10" t="n"/>
+      <c r="AS72" s="10" t="n"/>
+      <c r="AT72" s="10" t="n"/>
+      <c r="AU72" s="10" t="n"/>
+      <c r="AV72" s="10" t="n"/>
+      <c r="AW72" s="10" t="n"/>
+      <c r="AX72" s="10" t="n"/>
+      <c r="AY72" s="10" t="n"/>
+      <c r="AZ72" s="10" t="n"/>
+      <c r="BA72" s="10" t="n"/>
+      <c r="BB72" s="10" t="n"/>
+      <c r="BC72" s="10" t="n"/>
+      <c r="BD72" s="10" t="n"/>
+      <c r="BE72" s="10" t="n"/>
+      <c r="BF72" s="10" t="n"/>
+      <c r="BG72" s="10" t="n"/>
+      <c r="BH72" s="10" t="n"/>
+      <c r="BI72" s="10" t="n"/>
+      <c r="BJ72" s="10" t="n"/>
+      <c r="BK72" s="10" t="n"/>
+      <c r="BL72" s="10" t="n"/>
+      <c r="BM72" s="10" t="n"/>
+      <c r="BN72" s="10" t="n"/>
+      <c r="BO72" s="10" t="n"/>
+      <c r="BP72" s="10" t="n"/>
+      <c r="BQ72" s="11" t="n"/>
+    </row>
+    <row r="73" ht="80" customHeight="1">
+      <c r="A73" s="44" t="n">
+        <v>52</v>
+      </c>
+      <c r="B73" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-016-052</t>
+        </is>
+      </c>
+      <c r="C73" s="10" t="n"/>
+      <c r="D73" s="11" t="n"/>
+      <c r="E73" s="46" t="inlineStr">
+        <is>
+          <t>Ngày áp dụng／Ngày ngừng — Nhập trên màn hình・loại trừ lẫn nhau・khả dụng theo chế độ</t>
+        </is>
+      </c>
+      <c r="F73" s="10" t="n"/>
+      <c r="G73" s="10" t="n"/>
+      <c r="H73" s="10" t="n"/>
+      <c r="I73" s="11" t="n"/>
+      <c r="J73" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN (có `dokusya.import`)
+・Đã tải template (50 cột)</t>
+        </is>
+      </c>
+      <c r="K73" s="10" t="n"/>
+      <c r="L73" s="10" t="n"/>
+      <c r="M73" s="10" t="n"/>
+      <c r="N73" s="10" t="n"/>
+      <c r="O73" s="10" t="n"/>
+      <c r="P73" s="11" t="n"/>
+      <c r="Q73" s="46" t="inlineStr"/>
+      <c r="R73" s="10" t="n"/>
+      <c r="S73" s="10" t="n"/>
+      <c r="T73" s="10" t="n"/>
+      <c r="U73" s="10" t="n"/>
+      <c r="V73" s="10" t="n"/>
+      <c r="W73" s="11" t="n"/>
+      <c r="X73" s="46" t="inlineStr"/>
+      <c r="Y73" s="10" t="n"/>
+      <c r="Z73" s="10" t="n"/>
+      <c r="AA73" s="10" t="n"/>
+      <c r="AB73" s="10" t="n"/>
+      <c r="AC73" s="10" t="n"/>
+      <c r="AD73" s="11" t="n"/>
+      <c r="AE73" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF73" s="11" t="n"/>
+      <c r="AG73" s="45" t="inlineStr"/>
+      <c r="AH73" s="10" t="n"/>
+      <c r="AI73" s="11" t="n"/>
+      <c r="AJ73" s="45" t="inlineStr"/>
+      <c r="AK73" s="10" t="n"/>
+      <c r="AL73" s="11" t="n"/>
+      <c r="AM73" s="45" t="inlineStr"/>
+      <c r="AN73" s="10" t="n"/>
+      <c r="AO73" s="11" t="n"/>
+      <c r="AP73" s="45" t="inlineStr"/>
+      <c r="AQ73" s="10" t="n"/>
+      <c r="AR73" s="11" t="n"/>
+      <c r="AS73" s="45" t="inlineStr"/>
+      <c r="AT73" s="10" t="n"/>
+      <c r="AU73" s="11" t="n"/>
+      <c r="AV73" s="45" t="inlineStr"/>
+      <c r="AW73" s="10" t="n"/>
+      <c r="AX73" s="11" t="n"/>
+      <c r="AY73" s="45" t="inlineStr"/>
+      <c r="AZ73" s="10" t="n"/>
+      <c r="BA73" s="11" t="n"/>
+      <c r="BB73" s="45" t="inlineStr"/>
+      <c r="BC73" s="10" t="n"/>
+      <c r="BD73" s="11" t="n"/>
+      <c r="BE73" s="45" t="inlineStr"/>
+      <c r="BF73" s="10" t="n"/>
+      <c r="BG73" s="11" t="n"/>
+      <c r="BH73" s="45" t="inlineStr"/>
+      <c r="BI73" s="10" t="n"/>
+      <c r="BJ73" s="11" t="n"/>
+      <c r="BK73" s="46" t="inlineStr"/>
+      <c r="BL73" s="10" t="n"/>
+      <c r="BM73" s="10" t="n"/>
+      <c r="BN73" s="10" t="n"/>
+      <c r="BO73" s="10" t="n"/>
+      <c r="BP73" s="10" t="n"/>
+      <c r="BQ73" s="11" t="n"/>
+    </row>
+    <row r="74" ht="80" customHeight="1">
+      <c r="A74" s="44" t="n">
+        <v>53</v>
+      </c>
+      <c r="B74" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-016-053</t>
+        </is>
+      </c>
+      <c r="C74" s="10" t="n"/>
+      <c r="D74" s="11" t="n"/>
+      <c r="E74" s="46" t="inlineStr">
+        <is>
+          <t>Cập nhật — Quy tắc ngày áp dụng theo loại đăng ký và khóa các mục ảnh hưởng đến báo biểu</t>
+        </is>
+      </c>
+      <c r="F74" s="10" t="n"/>
+      <c r="G74" s="10" t="n"/>
+      <c r="H74" s="10" t="n"/>
+      <c r="I74" s="11" t="n"/>
+      <c r="J74" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN
+・Dữ liệu chuẩn bị: người đọc hiện có của bản giấy・bản điện tử (ngày bắt đầu đọc báo ở quá khứ)</t>
+        </is>
+      </c>
+      <c r="K74" s="10" t="n"/>
+      <c r="L74" s="10" t="n"/>
+      <c r="M74" s="10" t="n"/>
+      <c r="N74" s="10" t="n"/>
+      <c r="O74" s="10" t="n"/>
+      <c r="P74" s="11" t="n"/>
+      <c r="Q74" s="46" t="inlineStr"/>
+      <c r="R74" s="10" t="n"/>
+      <c r="S74" s="10" t="n"/>
+      <c r="T74" s="10" t="n"/>
+      <c r="U74" s="10" t="n"/>
+      <c r="V74" s="10" t="n"/>
+      <c r="W74" s="11" t="n"/>
+      <c r="X74" s="46" t="inlineStr"/>
+      <c r="Y74" s="10" t="n"/>
+      <c r="Z74" s="10" t="n"/>
+      <c r="AA74" s="10" t="n"/>
+      <c r="AB74" s="10" t="n"/>
+      <c r="AC74" s="10" t="n"/>
+      <c r="AD74" s="11" t="n"/>
+      <c r="AE74" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF74" s="11" t="n"/>
+      <c r="AG74" s="45" t="inlineStr"/>
+      <c r="AH74" s="10" t="n"/>
+      <c r="AI74" s="11" t="n"/>
+      <c r="AJ74" s="45" t="inlineStr"/>
+      <c r="AK74" s="10" t="n"/>
+      <c r="AL74" s="11" t="n"/>
+      <c r="AM74" s="45" t="inlineStr"/>
+      <c r="AN74" s="10" t="n"/>
+      <c r="AO74" s="11" t="n"/>
+      <c r="AP74" s="45" t="inlineStr"/>
+      <c r="AQ74" s="10" t="n"/>
+      <c r="AR74" s="11" t="n"/>
+      <c r="AS74" s="45" t="inlineStr"/>
+      <c r="AT74" s="10" t="n"/>
+      <c r="AU74" s="11" t="n"/>
+      <c r="AV74" s="45" t="inlineStr"/>
+      <c r="AW74" s="10" t="n"/>
+      <c r="AX74" s="11" t="n"/>
+      <c r="AY74" s="45" t="inlineStr"/>
+      <c r="AZ74" s="10" t="n"/>
+      <c r="BA74" s="11" t="n"/>
+      <c r="BB74" s="45" t="inlineStr"/>
+      <c r="BC74" s="10" t="n"/>
+      <c r="BD74" s="11" t="n"/>
+      <c r="BE74" s="45" t="inlineStr"/>
+      <c r="BF74" s="10" t="n"/>
+      <c r="BG74" s="11" t="n"/>
+      <c r="BH74" s="45" t="inlineStr"/>
+      <c r="BI74" s="10" t="n"/>
+      <c r="BJ74" s="11" t="n"/>
+      <c r="BK74" s="46" t="inlineStr"/>
+      <c r="BL74" s="10" t="n"/>
+      <c r="BM74" s="10" t="n"/>
+      <c r="BN74" s="10" t="n"/>
+      <c r="BO74" s="10" t="n"/>
+      <c r="BP74" s="10" t="n"/>
+      <c r="BQ74" s="11" t="n"/>
+    </row>
+    <row r="75" ht="64" customHeight="1">
+      <c r="A75" s="44" t="n">
+        <v>54</v>
+      </c>
+      <c r="B75" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-016-054</t>
+        </is>
+      </c>
+      <c r="C75" s="10" t="n"/>
+      <c r="D75" s="11" t="n"/>
+      <c r="E75" s="46" t="inlineStr">
+        <is>
+          <t>Ngừng hàng loạt — Tạo đặt trước hủy (bản giấy・không liên kết)</t>
+        </is>
+      </c>
+      <c r="F75" s="10" t="n"/>
+      <c r="G75" s="10" t="n"/>
+      <c r="H75" s="10" t="n"/>
+      <c r="I75" s="11" t="n"/>
+      <c r="J75" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN
+・Dữ liệu chuẩn bị: người đọc hiện có của bản giấy (đang đọc báo・số bản đọc=3)</t>
+        </is>
+      </c>
+      <c r="K75" s="10" t="n"/>
+      <c r="L75" s="10" t="n"/>
+      <c r="M75" s="10" t="n"/>
+      <c r="N75" s="10" t="n"/>
+      <c r="O75" s="10" t="n"/>
+      <c r="P75" s="11" t="n"/>
+      <c r="Q75" s="46" t="inlineStr"/>
+      <c r="R75" s="10" t="n"/>
+      <c r="S75" s="10" t="n"/>
+      <c r="T75" s="10" t="n"/>
+      <c r="U75" s="10" t="n"/>
+      <c r="V75" s="10" t="n"/>
+      <c r="W75" s="11" t="n"/>
+      <c r="X75" s="46" t="inlineStr"/>
+      <c r="Y75" s="10" t="n"/>
+      <c r="Z75" s="10" t="n"/>
+      <c r="AA75" s="10" t="n"/>
+      <c r="AB75" s="10" t="n"/>
+      <c r="AC75" s="10" t="n"/>
+      <c r="AD75" s="11" t="n"/>
+      <c r="AE75" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF75" s="11" t="n"/>
+      <c r="AG75" s="45" t="inlineStr"/>
+      <c r="AH75" s="10" t="n"/>
+      <c r="AI75" s="11" t="n"/>
+      <c r="AJ75" s="45" t="inlineStr"/>
+      <c r="AK75" s="10" t="n"/>
+      <c r="AL75" s="11" t="n"/>
+      <c r="AM75" s="45" t="inlineStr"/>
+      <c r="AN75" s="10" t="n"/>
+      <c r="AO75" s="11" t="n"/>
+      <c r="AP75" s="45" t="inlineStr"/>
+      <c r="AQ75" s="10" t="n"/>
+      <c r="AR75" s="11" t="n"/>
+      <c r="AS75" s="45" t="inlineStr"/>
+      <c r="AT75" s="10" t="n"/>
+      <c r="AU75" s="11" t="n"/>
+      <c r="AV75" s="45" t="inlineStr"/>
+      <c r="AW75" s="10" t="n"/>
+      <c r="AX75" s="11" t="n"/>
+      <c r="AY75" s="45" t="inlineStr"/>
+      <c r="AZ75" s="10" t="n"/>
+      <c r="BA75" s="11" t="n"/>
+      <c r="BB75" s="45" t="inlineStr"/>
+      <c r="BC75" s="10" t="n"/>
+      <c r="BD75" s="11" t="n"/>
+      <c r="BE75" s="45" t="inlineStr"/>
+      <c r="BF75" s="10" t="n"/>
+      <c r="BG75" s="11" t="n"/>
+      <c r="BH75" s="45" t="inlineStr"/>
+      <c r="BI75" s="10" t="n"/>
+      <c r="BJ75" s="11" t="n"/>
+      <c r="BK75" s="46" t="inlineStr"/>
+      <c r="BL75" s="10" t="n"/>
+      <c r="BM75" s="10" t="n"/>
+      <c r="BN75" s="10" t="n"/>
+      <c r="BO75" s="10" t="n"/>
+      <c r="BP75" s="10" t="n"/>
+      <c r="BQ75" s="11" t="n"/>
+    </row>
+    <row r="76" ht="176" customHeight="1">
+      <c r="A76" s="44" t="n">
+        <v>55</v>
+      </c>
+      <c r="B76" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-016-055</t>
+        </is>
+      </c>
+      <c r="C76" s="10" t="n"/>
+      <c r="D76" s="11" t="n"/>
+      <c r="E76" s="46" t="inlineStr">
+        <is>
+          <t>Ngừng hàng loạt — Liên kết bản điện tử thất bại thì rollback toàn bộ ＋ gửi bù trừ</t>
+        </is>
+      </c>
+      <c r="F76" s="10" t="n"/>
+      <c r="G76" s="10" t="n"/>
+      <c r="H76" s="10" t="n"/>
+      <c r="I76" s="11" t="n"/>
+      <c r="J76" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN
+・Dữ liệu chuẩn bị: 3 người đọc hiện có của bản điện tử (có ID hội viên bản điện tử・không phải thẻ tín dụng)
+・Liên kết bản điện tử đang bật (DENSHIBAN_PUSH_ENABLED=true)
+・Thiết lập môi trường giả lập để liên kết của bản ghi thứ 3 trả về lỗi</t>
+        </is>
+      </c>
+      <c r="K76" s="10" t="n"/>
+      <c r="L76" s="10" t="n"/>
+      <c r="M76" s="10" t="n"/>
+      <c r="N76" s="10" t="n"/>
+      <c r="O76" s="10" t="n"/>
+      <c r="P76" s="11" t="n"/>
+      <c r="Q76" s="46" t="inlineStr"/>
+      <c r="R76" s="10" t="n"/>
+      <c r="S76" s="10" t="n"/>
+      <c r="T76" s="10" t="n"/>
+      <c r="U76" s="10" t="n"/>
+      <c r="V76" s="10" t="n"/>
+      <c r="W76" s="11" t="n"/>
+      <c r="X76" s="46" t="inlineStr"/>
+      <c r="Y76" s="10" t="n"/>
+      <c r="Z76" s="10" t="n"/>
+      <c r="AA76" s="10" t="n"/>
+      <c r="AB76" s="10" t="n"/>
+      <c r="AC76" s="10" t="n"/>
+      <c r="AD76" s="11" t="n"/>
+      <c r="AE76" s="45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF76" s="11" t="n"/>
+      <c r="AG76" s="45" t="inlineStr"/>
+      <c r="AH76" s="10" t="n"/>
+      <c r="AI76" s="11" t="n"/>
+      <c r="AJ76" s="45" t="inlineStr"/>
+      <c r="AK76" s="10" t="n"/>
+      <c r="AL76" s="11" t="n"/>
+      <c r="AM76" s="45" t="inlineStr"/>
+      <c r="AN76" s="10" t="n"/>
+      <c r="AO76" s="11" t="n"/>
+      <c r="AP76" s="45" t="inlineStr"/>
+      <c r="AQ76" s="10" t="n"/>
+      <c r="AR76" s="11" t="n"/>
+      <c r="AS76" s="45" t="inlineStr"/>
+      <c r="AT76" s="10" t="n"/>
+      <c r="AU76" s="11" t="n"/>
+      <c r="AV76" s="45" t="inlineStr"/>
+      <c r="AW76" s="10" t="n"/>
+      <c r="AX76" s="11" t="n"/>
+      <c r="AY76" s="45" t="inlineStr"/>
+      <c r="AZ76" s="10" t="n"/>
+      <c r="BA76" s="11" t="n"/>
+      <c r="BB76" s="45" t="inlineStr"/>
+      <c r="BC76" s="10" t="n"/>
+      <c r="BD76" s="11" t="n"/>
+      <c r="BE76" s="45" t="inlineStr"/>
+      <c r="BF76" s="10" t="n"/>
+      <c r="BG76" s="11" t="n"/>
+      <c r="BH76" s="45" t="inlineStr"/>
+      <c r="BI76" s="10" t="n"/>
+      <c r="BJ76" s="11" t="n"/>
+      <c r="BK76" s="46" t="inlineStr"/>
+      <c r="BL76" s="10" t="n"/>
+      <c r="BM76" s="10" t="n"/>
+      <c r="BN76" s="10" t="n"/>
+      <c r="BO76" s="10" t="n"/>
+      <c r="BP76" s="10" t="n"/>
+      <c r="BQ76" s="11" t="n"/>
+    </row>
+    <row r="77" ht="64" customHeight="1">
+      <c r="A77" s="44" t="n">
+        <v>56</v>
+      </c>
+      <c r="B77" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-016-056</t>
+        </is>
+      </c>
+      <c r="C77" s="10" t="n"/>
+      <c r="D77" s="11" t="n"/>
+      <c r="E77" s="46" t="inlineStr">
+        <is>
+          <t>Cột nhập — 4 mục phụ thuộc của phân loại tầng lớp người đọc (#56405)</t>
+        </is>
+      </c>
+      <c r="F77" s="10" t="n"/>
+      <c r="G77" s="10" t="n"/>
+      <c r="H77" s="10" t="n"/>
+      <c r="I77" s="11" t="n"/>
+      <c r="J77" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN (ja_id=100, có quyền `dokusya.import`)
+・Đã tải template bản mới nhất</t>
+        </is>
+      </c>
+      <c r="K77" s="10" t="n"/>
+      <c r="L77" s="10" t="n"/>
+      <c r="M77" s="10" t="n"/>
+      <c r="N77" s="10" t="n"/>
+      <c r="O77" s="10" t="n"/>
+      <c r="P77" s="11" t="n"/>
+      <c r="Q77" s="46" t="inlineStr"/>
+      <c r="R77" s="10" t="n"/>
+      <c r="S77" s="10" t="n"/>
+      <c r="T77" s="10" t="n"/>
+      <c r="U77" s="10" t="n"/>
+      <c r="V77" s="10" t="n"/>
+      <c r="W77" s="11" t="n"/>
+      <c r="X77" s="46" t="inlineStr"/>
+      <c r="Y77" s="10" t="n"/>
+      <c r="Z77" s="10" t="n"/>
+      <c r="AA77" s="10" t="n"/>
+      <c r="AB77" s="10" t="n"/>
+      <c r="AC77" s="10" t="n"/>
+      <c r="AD77" s="11" t="n"/>
+      <c r="AE77" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF77" s="11" t="n"/>
+      <c r="AG77" s="45" t="inlineStr"/>
+      <c r="AH77" s="10" t="n"/>
+      <c r="AI77" s="11" t="n"/>
+      <c r="AJ77" s="45" t="inlineStr"/>
+      <c r="AK77" s="10" t="n"/>
+      <c r="AL77" s="11" t="n"/>
+      <c r="AM77" s="45" t="inlineStr"/>
+      <c r="AN77" s="10" t="n"/>
+      <c r="AO77" s="11" t="n"/>
+      <c r="AP77" s="45" t="inlineStr"/>
+      <c r="AQ77" s="10" t="n"/>
+      <c r="AR77" s="11" t="n"/>
+      <c r="AS77" s="45" t="inlineStr"/>
+      <c r="AT77" s="10" t="n"/>
+      <c r="AU77" s="11" t="n"/>
+      <c r="AV77" s="45" t="inlineStr"/>
+      <c r="AW77" s="10" t="n"/>
+      <c r="AX77" s="11" t="n"/>
+      <c r="AY77" s="45" t="inlineStr"/>
+      <c r="AZ77" s="10" t="n"/>
+      <c r="BA77" s="11" t="n"/>
+      <c r="BB77" s="45" t="inlineStr"/>
+      <c r="BC77" s="10" t="n"/>
+      <c r="BD77" s="11" t="n"/>
+      <c r="BE77" s="45" t="inlineStr"/>
+      <c r="BF77" s="10" t="n"/>
+      <c r="BG77" s="11" t="n"/>
+      <c r="BH77" s="45" t="inlineStr"/>
+      <c r="BI77" s="10" t="n"/>
+      <c r="BJ77" s="11" t="n"/>
+      <c r="BK77" s="46" t="inlineStr"/>
+      <c r="BL77" s="10" t="n"/>
+      <c r="BM77" s="10" t="n"/>
+      <c r="BN77" s="10" t="n"/>
+      <c r="BO77" s="10" t="n"/>
+      <c r="BP77" s="10" t="n"/>
+      <c r="BQ77" s="11" t="n"/>
+    </row>
+    <row r="78" ht="224" customHeight="1">
+      <c r="A78" s="44" t="n">
+        <v>57</v>
+      </c>
+      <c r="B78" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-016-057</t>
+        </is>
+      </c>
+      <c r="C78" s="10" t="n"/>
+      <c r="D78" s="11" t="n"/>
+      <c r="E78" s="46" t="inlineStr">
+        <is>
+          <t>Kiểm tra khi nhập — Trùng lặp email được đánh giá xuyên JA (#56568)</t>
+        </is>
+      </c>
+      <c r="F78" s="10" t="n"/>
+      <c r="G78" s="10" t="n"/>
+      <c r="H78" s="10" t="n"/>
+      <c r="I78" s="11" t="n"/>
+      <c r="J78" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN (ja_id=100, có quyền `dokusya.import`)
+・Ở **JA khác** (ja_id=200) tồn tại người đọc loại đăng ký=bản điện tử・email `dup@example.com`
+・Ở JA của mình (ja_id=100) tồn tại người đọc loại đăng ký=bản giấy・email `paper@example.com`
+・Ở JA khác (ja_id=200) tồn tại người đọc loại đăng ký=bản điện tử・email `deleted@example.com` **đã xóa logic**</t>
+        </is>
+      </c>
+      <c r="K78" s="10" t="n"/>
+      <c r="L78" s="10" t="n"/>
+      <c r="M78" s="10" t="n"/>
+      <c r="N78" s="10" t="n"/>
+      <c r="O78" s="10" t="n"/>
+      <c r="P78" s="11" t="n"/>
+      <c r="Q78" s="46" t="inlineStr"/>
+      <c r="R78" s="10" t="n"/>
+      <c r="S78" s="10" t="n"/>
+      <c r="T78" s="10" t="n"/>
+      <c r="U78" s="10" t="n"/>
+      <c r="V78" s="10" t="n"/>
+      <c r="W78" s="11" t="n"/>
+      <c r="X78" s="46" t="inlineStr"/>
+      <c r="Y78" s="10" t="n"/>
+      <c r="Z78" s="10" t="n"/>
+      <c r="AA78" s="10" t="n"/>
+      <c r="AB78" s="10" t="n"/>
+      <c r="AC78" s="10" t="n"/>
+      <c r="AD78" s="11" t="n"/>
+      <c r="AE78" s="45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF78" s="11" t="n"/>
+      <c r="AG78" s="45" t="inlineStr"/>
+      <c r="AH78" s="10" t="n"/>
+      <c r="AI78" s="11" t="n"/>
+      <c r="AJ78" s="45" t="inlineStr"/>
+      <c r="AK78" s="10" t="n"/>
+      <c r="AL78" s="11" t="n"/>
+      <c r="AM78" s="45" t="inlineStr"/>
+      <c r="AN78" s="10" t="n"/>
+      <c r="AO78" s="11" t="n"/>
+      <c r="AP78" s="45" t="inlineStr"/>
+      <c r="AQ78" s="10" t="n"/>
+      <c r="AR78" s="11" t="n"/>
+      <c r="AS78" s="45" t="inlineStr"/>
+      <c r="AT78" s="10" t="n"/>
+      <c r="AU78" s="11" t="n"/>
+      <c r="AV78" s="45" t="inlineStr"/>
+      <c r="AW78" s="10" t="n"/>
+      <c r="AX78" s="11" t="n"/>
+      <c r="AY78" s="45" t="inlineStr"/>
+      <c r="AZ78" s="10" t="n"/>
+      <c r="BA78" s="11" t="n"/>
+      <c r="BB78" s="45" t="inlineStr"/>
+      <c r="BC78" s="10" t="n"/>
+      <c r="BD78" s="11" t="n"/>
+      <c r="BE78" s="45" t="inlineStr"/>
+      <c r="BF78" s="10" t="n"/>
+      <c r="BG78" s="11" t="n"/>
+      <c r="BH78" s="45" t="inlineStr"/>
+      <c r="BI78" s="10" t="n"/>
+      <c r="BJ78" s="11" t="n"/>
+      <c r="BK78" s="46" t="inlineStr"/>
+      <c r="BL78" s="10" t="n"/>
+      <c r="BM78" s="10" t="n"/>
+      <c r="BN78" s="10" t="n"/>
+      <c r="BO78" s="10" t="n"/>
+      <c r="BP78" s="10" t="n"/>
+      <c r="BQ78" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="942">
+  <mergeCells count="1045">
     <mergeCell ref="AS59:AU59"/>
     <mergeCell ref="J31:P31"/>
     <mergeCell ref="B60:D60"/>
@@ -18174,21 +18853,29 @@
     <mergeCell ref="AM65:AO65"/>
     <mergeCell ref="AG24:AI24"/>
     <mergeCell ref="BH39:BJ39"/>
+    <mergeCell ref="BB77:BD77"/>
     <mergeCell ref="W2:AH2"/>
     <mergeCell ref="X10:AD11"/>
     <mergeCell ref="A26:BQ26"/>
     <mergeCell ref="AG42:AI42"/>
     <mergeCell ref="BK70:BQ70"/>
     <mergeCell ref="AJ22:AL22"/>
+    <mergeCell ref="AY74:BA74"/>
     <mergeCell ref="AP13:AR13"/>
+    <mergeCell ref="AS74:AU74"/>
+    <mergeCell ref="AV75:AX75"/>
     <mergeCell ref="BK42:BQ42"/>
     <mergeCell ref="Q38:W38"/>
+    <mergeCell ref="Q76:W76"/>
     <mergeCell ref="AE34:AF34"/>
+    <mergeCell ref="AY76:BA76"/>
     <mergeCell ref="AJ51:AL51"/>
     <mergeCell ref="AP71:AR71"/>
     <mergeCell ref="BK47:BQ47"/>
     <mergeCell ref="E25:I25"/>
+    <mergeCell ref="X74:AD74"/>
     <mergeCell ref="X68:AD68"/>
+    <mergeCell ref="AS76:AU76"/>
     <mergeCell ref="AE36:AF36"/>
     <mergeCell ref="AS51:AU51"/>
     <mergeCell ref="Q15:W15"/>
@@ -18199,16 +18886,21 @@
     <mergeCell ref="BH21:BJ21"/>
     <mergeCell ref="AM34:AO34"/>
     <mergeCell ref="AJ38:AL38"/>
+    <mergeCell ref="AP73:AR73"/>
+    <mergeCell ref="X76:AD76"/>
+    <mergeCell ref="J75:P75"/>
     <mergeCell ref="BE35:BG35"/>
     <mergeCell ref="BK48:BQ48"/>
     <mergeCell ref="AM49:AO49"/>
     <mergeCell ref="AE50:AF50"/>
     <mergeCell ref="X69:AD69"/>
+    <mergeCell ref="B73:D73"/>
     <mergeCell ref="BE22:BG22"/>
     <mergeCell ref="BH23:BJ23"/>
     <mergeCell ref="AE31:AF31"/>
     <mergeCell ref="H7:J7"/>
     <mergeCell ref="AG45:AI45"/>
+    <mergeCell ref="AM78:AO78"/>
     <mergeCell ref="AS67:AU67"/>
     <mergeCell ref="AY29:BA29"/>
     <mergeCell ref="E20:I20"/>
@@ -18217,6 +18909,7 @@
     <mergeCell ref="J39:P39"/>
     <mergeCell ref="X21:AD21"/>
     <mergeCell ref="AE62:AF62"/>
+    <mergeCell ref="B74:D74"/>
     <mergeCell ref="AG47:AI47"/>
     <mergeCell ref="B68:D68"/>
     <mergeCell ref="AF8:AH8"/>
@@ -18224,11 +18917,14 @@
     <mergeCell ref="AY31:BA31"/>
     <mergeCell ref="AJ35:AL35"/>
     <mergeCell ref="BK37:BQ37"/>
+    <mergeCell ref="Q77:W77"/>
+    <mergeCell ref="E78:I78"/>
     <mergeCell ref="AM55:AO55"/>
     <mergeCell ref="BH34:BJ34"/>
     <mergeCell ref="X23:AD23"/>
     <mergeCell ref="BE38:BG38"/>
     <mergeCell ref="AE64:AF64"/>
+    <mergeCell ref="B76:D76"/>
     <mergeCell ref="AS62:AU62"/>
     <mergeCell ref="AV63:AX63"/>
     <mergeCell ref="AP66:AR66"/>
@@ -18267,9 +18963,11 @@
     <mergeCell ref="W3:AH3"/>
     <mergeCell ref="E33:I33"/>
     <mergeCell ref="Q48:W48"/>
+    <mergeCell ref="AE75:AF75"/>
     <mergeCell ref="AV13:AX13"/>
     <mergeCell ref="BH42:BJ42"/>
     <mergeCell ref="AS17:AU17"/>
+    <mergeCell ref="AV78:AX78"/>
     <mergeCell ref="AS11:AU11"/>
     <mergeCell ref="BH29:BJ29"/>
     <mergeCell ref="Q41:W41"/>
@@ -18277,11 +18975,14 @@
     <mergeCell ref="AV53:AX53"/>
     <mergeCell ref="AS19:AU19"/>
     <mergeCell ref="Q56:W56"/>
+    <mergeCell ref="AS75:AU75"/>
+    <mergeCell ref="X77:AD77"/>
     <mergeCell ref="Q43:W43"/>
     <mergeCell ref="J14:P14"/>
     <mergeCell ref="AE39:AF39"/>
     <mergeCell ref="B51:D51"/>
     <mergeCell ref="A18:BQ18"/>
+    <mergeCell ref="E74:I74"/>
     <mergeCell ref="AM50:AO50"/>
     <mergeCell ref="AJ54:AL54"/>
     <mergeCell ref="AM15:AO15"/>
@@ -18291,6 +18992,7 @@
     <mergeCell ref="BE34:BG34"/>
     <mergeCell ref="BE28:BG28"/>
     <mergeCell ref="AJ41:AL41"/>
+    <mergeCell ref="J78:P78"/>
     <mergeCell ref="H8:J8"/>
     <mergeCell ref="BK10:BQ11"/>
     <mergeCell ref="J53:P53"/>
@@ -18315,6 +19017,7 @@
     <mergeCell ref="BK68:BQ68"/>
     <mergeCell ref="A44:BQ44"/>
     <mergeCell ref="AY47:BA47"/>
+    <mergeCell ref="B77:D77"/>
     <mergeCell ref="E21:I21"/>
     <mergeCell ref="BH50:BJ50"/>
     <mergeCell ref="Q36:W36"/>
@@ -18341,8 +19044,10 @@
     <mergeCell ref="X27:AD27"/>
     <mergeCell ref="AG66:AI66"/>
     <mergeCell ref="BB46:BD46"/>
+    <mergeCell ref="AM74:AO74"/>
     <mergeCell ref="B24:D24"/>
     <mergeCell ref="AY60:BA60"/>
+    <mergeCell ref="AG74:AI74"/>
     <mergeCell ref="AV15:AX15"/>
     <mergeCell ref="AY16:BA16"/>
     <mergeCell ref="Q62:W62"/>
@@ -18350,6 +19055,7 @@
     <mergeCell ref="BB48:BD48"/>
     <mergeCell ref="AG68:AI68"/>
     <mergeCell ref="AG43:AI43"/>
+    <mergeCell ref="AM76:AO76"/>
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="E49:I49"/>
     <mergeCell ref="J68:P68"/>
@@ -18363,6 +19069,7 @@
     <mergeCell ref="AV65:AX65"/>
     <mergeCell ref="BH45:BJ45"/>
     <mergeCell ref="AS20:AU20"/>
+    <mergeCell ref="E76:I76"/>
     <mergeCell ref="AP24:AR24"/>
     <mergeCell ref="BH32:BJ32"/>
     <mergeCell ref="B27:D27"/>
@@ -18370,6 +19077,7 @@
     <mergeCell ref="BH47:BJ47"/>
     <mergeCell ref="AS22:AU22"/>
     <mergeCell ref="X20:AD20"/>
+    <mergeCell ref="BH74:BJ74"/>
     <mergeCell ref="X14:AD14"/>
     <mergeCell ref="AY42:BA42"/>
     <mergeCell ref="AE55:AF55"/>
@@ -18379,6 +19087,7 @@
     <mergeCell ref="BH46:BJ46"/>
     <mergeCell ref="BE50:BG50"/>
     <mergeCell ref="AP19:AR19"/>
+    <mergeCell ref="BH76:BJ76"/>
     <mergeCell ref="BE31:BG31"/>
     <mergeCell ref="J21:P21"/>
     <mergeCell ref="A1:E1"/>
@@ -18391,25 +19100,33 @@
     <mergeCell ref="B37:D37"/>
     <mergeCell ref="BH58:BJ58"/>
     <mergeCell ref="AV28:AX28"/>
+    <mergeCell ref="Q75:W75"/>
     <mergeCell ref="AY48:BA48"/>
     <mergeCell ref="BB49:BD49"/>
     <mergeCell ref="AG62:AI62"/>
     <mergeCell ref="AE33:AF33"/>
     <mergeCell ref="BB36:BD36"/>
+    <mergeCell ref="AV74:AX74"/>
+    <mergeCell ref="AP77:AR77"/>
     <mergeCell ref="E31:I31"/>
     <mergeCell ref="AV36:AX36"/>
+    <mergeCell ref="BK77:BQ77"/>
     <mergeCell ref="T6:V6"/>
     <mergeCell ref="B20:D20"/>
+    <mergeCell ref="AE73:AF73"/>
     <mergeCell ref="Q39:W39"/>
     <mergeCell ref="AS33:AU33"/>
+    <mergeCell ref="AJ75:AL75"/>
     <mergeCell ref="AM36:AO36"/>
     <mergeCell ref="F1:Q1"/>
     <mergeCell ref="AP37:AR37"/>
     <mergeCell ref="J34:P34"/>
     <mergeCell ref="AY37:BA37"/>
     <mergeCell ref="BE65:BG65"/>
+    <mergeCell ref="J74:P74"/>
     <mergeCell ref="AS35:AU35"/>
     <mergeCell ref="J49:P49"/>
+    <mergeCell ref="AE74:AF74"/>
     <mergeCell ref="AE68:AF68"/>
     <mergeCell ref="J36:P36"/>
     <mergeCell ref="BB62:BD62"/>
@@ -18419,6 +19136,7 @@
     <mergeCell ref="AJ70:AL70"/>
     <mergeCell ref="AV21:AX21"/>
     <mergeCell ref="AY53:BA53"/>
+    <mergeCell ref="AM77:AO77"/>
     <mergeCell ref="BK24:BQ24"/>
     <mergeCell ref="X45:AD45"/>
     <mergeCell ref="E50:I50"/>
@@ -18435,8 +19153,11 @@
     <mergeCell ref="Q65:W65"/>
     <mergeCell ref="AY68:BA68"/>
     <mergeCell ref="BH71:BJ71"/>
+    <mergeCell ref="BE75:BG75"/>
+    <mergeCell ref="AG75:AI75"/>
     <mergeCell ref="X59:AD59"/>
     <mergeCell ref="K8:M8"/>
+    <mergeCell ref="BH73:BJ73"/>
     <mergeCell ref="BK19:BQ19"/>
     <mergeCell ref="AE21:AF21"/>
     <mergeCell ref="X46:AD46"/>
@@ -18455,17 +19176,20 @@
     <mergeCell ref="AE23:AF23"/>
     <mergeCell ref="AC6:AE6"/>
     <mergeCell ref="AG39:AI39"/>
+    <mergeCell ref="BH77:BJ77"/>
     <mergeCell ref="BB17:BD17"/>
     <mergeCell ref="AV49:AX49"/>
     <mergeCell ref="BB11:BD11"/>
     <mergeCell ref="AJ25:AL25"/>
     <mergeCell ref="B45:D45"/>
+    <mergeCell ref="BE78:BG78"/>
     <mergeCell ref="BE53:BG53"/>
     <mergeCell ref="AJ60:AL60"/>
     <mergeCell ref="AM32:AO32"/>
     <mergeCell ref="AG64:AI64"/>
     <mergeCell ref="Q7:S7"/>
     <mergeCell ref="J24:P24"/>
+    <mergeCell ref="BB75:BD75"/>
     <mergeCell ref="AG51:AI51"/>
     <mergeCell ref="Q20:W20"/>
     <mergeCell ref="B47:D47"/>
@@ -18479,6 +19203,7 @@
     <mergeCell ref="E32:I32"/>
     <mergeCell ref="BH66:BJ66"/>
     <mergeCell ref="AS41:AU41"/>
+    <mergeCell ref="Q78:W78"/>
     <mergeCell ref="AE49:AF49"/>
     <mergeCell ref="AY13:BA13"/>
     <mergeCell ref="Q8:S8"/>
@@ -18494,6 +19219,7 @@
     <mergeCell ref="X41:AD41"/>
     <mergeCell ref="AS43:AU43"/>
     <mergeCell ref="BH68:BJ68"/>
+    <mergeCell ref="AE76:AF76"/>
     <mergeCell ref="AY63:BA63"/>
     <mergeCell ref="BE25:BG25"/>
     <mergeCell ref="BK38:BQ38"/>
@@ -18506,6 +19232,7 @@
     <mergeCell ref="AS36:AU36"/>
     <mergeCell ref="J50:P50"/>
     <mergeCell ref="AM39:AO39"/>
+    <mergeCell ref="AJ78:AL78"/>
     <mergeCell ref="J42:P42"/>
     <mergeCell ref="BK63:BQ63"/>
     <mergeCell ref="AJ15:AL15"/>
@@ -18513,6 +19240,7 @@
     <mergeCell ref="Q13:W13"/>
     <mergeCell ref="AG19:AI19"/>
     <mergeCell ref="X36:AD36"/>
+    <mergeCell ref="AE77:AF77"/>
     <mergeCell ref="Q25:W25"/>
     <mergeCell ref="AV37:AX37"/>
     <mergeCell ref="BB65:BD65"/>
@@ -18532,6 +19260,7 @@
     <mergeCell ref="AG14:AI14"/>
     <mergeCell ref="B35:D35"/>
     <mergeCell ref="AV32:AX32"/>
+    <mergeCell ref="Q73:W73"/>
     <mergeCell ref="E45:I45"/>
     <mergeCell ref="AS29:AU29"/>
     <mergeCell ref="AM42:AO42"/>
@@ -18544,6 +19273,7 @@
     <mergeCell ref="AM23:AO23"/>
     <mergeCell ref="AE24:AF24"/>
     <mergeCell ref="J70:P70"/>
+    <mergeCell ref="A72:BQ72"/>
     <mergeCell ref="AV27:AX27"/>
     <mergeCell ref="BE55:BG55"/>
     <mergeCell ref="AS31:AU31"/>
@@ -18568,7 +19298,9 @@
     <mergeCell ref="BB60:BD60"/>
     <mergeCell ref="B69:D69"/>
     <mergeCell ref="A61:BQ61"/>
+    <mergeCell ref="J76:P76"/>
     <mergeCell ref="AP59:AR59"/>
+    <mergeCell ref="E73:I73"/>
     <mergeCell ref="AP46:AR46"/>
     <mergeCell ref="BK59:BQ59"/>
     <mergeCell ref="BK46:BQ46"/>
@@ -18591,8 +19323,10 @@
     <mergeCell ref="BE68:BG68"/>
     <mergeCell ref="AP43:AR43"/>
     <mergeCell ref="AM53:AO53"/>
+    <mergeCell ref="BE74:BG74"/>
     <mergeCell ref="AM47:AO47"/>
     <mergeCell ref="B10:D11"/>
+    <mergeCell ref="AY77:BA77"/>
     <mergeCell ref="J45:P45"/>
     <mergeCell ref="Q35:W35"/>
     <mergeCell ref="AM19:AO19"/>
@@ -18604,10 +19338,14 @@
     <mergeCell ref="AV71:AX71"/>
     <mergeCell ref="E53:I53"/>
     <mergeCell ref="AE70:AF70"/>
+    <mergeCell ref="BB73:BD73"/>
     <mergeCell ref="AM48:AO48"/>
+    <mergeCell ref="Q74:W74"/>
     <mergeCell ref="Q49:W49"/>
     <mergeCell ref="E68:I68"/>
     <mergeCell ref="BK43:BQ43"/>
+    <mergeCell ref="AV73:AX73"/>
+    <mergeCell ref="AV76:AX76"/>
     <mergeCell ref="AF6:AH6"/>
     <mergeCell ref="E55:I55"/>
     <mergeCell ref="AE32:AF32"/>
@@ -18627,6 +19365,8 @@
     <mergeCell ref="AY59:BA59"/>
     <mergeCell ref="AS70:AU70"/>
     <mergeCell ref="J71:P71"/>
+    <mergeCell ref="AM73:AO73"/>
+    <mergeCell ref="AV77:AX77"/>
     <mergeCell ref="J58:P58"/>
     <mergeCell ref="AS32:AU32"/>
     <mergeCell ref="AM45:AO45"/>
@@ -18638,12 +19378,14 @@
     <mergeCell ref="BE23:BG23"/>
     <mergeCell ref="AJ36:AL36"/>
     <mergeCell ref="BK36:BQ36"/>
+    <mergeCell ref="J73:P73"/>
     <mergeCell ref="AS47:AU47"/>
     <mergeCell ref="AY54:BA54"/>
     <mergeCell ref="AJ29:AL29"/>
     <mergeCell ref="AG33:AI33"/>
     <mergeCell ref="X17:AD17"/>
     <mergeCell ref="Q54:W54"/>
+    <mergeCell ref="J77:P77"/>
     <mergeCell ref="AS65:AU65"/>
     <mergeCell ref="AY27:BA27"/>
     <mergeCell ref="AJ31:AL31"/>
@@ -18680,6 +19422,8 @@
     <mergeCell ref="AG59:AI59"/>
     <mergeCell ref="BK64:BQ64"/>
     <mergeCell ref="J66:P66"/>
+    <mergeCell ref="BE76:BG76"/>
+    <mergeCell ref="AG76:AI76"/>
     <mergeCell ref="BK51:BQ51"/>
     <mergeCell ref="AM67:AO67"/>
     <mergeCell ref="X60:AD60"/>
@@ -18696,6 +19440,7 @@
     <mergeCell ref="AP65:AR65"/>
     <mergeCell ref="AM20:AO20"/>
     <mergeCell ref="AM69:AO69"/>
+    <mergeCell ref="BE77:BG77"/>
     <mergeCell ref="AJ24:AL24"/>
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="AY11:BA11"/>
@@ -18704,15 +19449,20 @@
     <mergeCell ref="AS13:AU13"/>
     <mergeCell ref="E69:I69"/>
     <mergeCell ref="AP17:AR17"/>
+    <mergeCell ref="AS78:AU78"/>
     <mergeCell ref="Q42:W42"/>
     <mergeCell ref="A12:BQ12"/>
     <mergeCell ref="AY15:BA15"/>
     <mergeCell ref="AS53:AU53"/>
+    <mergeCell ref="BB76:BD76"/>
     <mergeCell ref="AG23:AI23"/>
+    <mergeCell ref="E77:I77"/>
     <mergeCell ref="X13:AD13"/>
     <mergeCell ref="AS15:AU15"/>
     <mergeCell ref="AE48:AF48"/>
+    <mergeCell ref="AP75:AR75"/>
     <mergeCell ref="BH27:BJ27"/>
+    <mergeCell ref="BK75:BQ75"/>
     <mergeCell ref="AS55:AU55"/>
     <mergeCell ref="BE37:BG37"/>
     <mergeCell ref="AJ50:AL50"/>
@@ -18725,11 +19475,13 @@
     <mergeCell ref="BB28:BD28"/>
     <mergeCell ref="AG41:AI41"/>
     <mergeCell ref="BH69:BJ69"/>
+    <mergeCell ref="AS73:AU73"/>
     <mergeCell ref="BH35:BJ35"/>
     <mergeCell ref="AP39:AR39"/>
     <mergeCell ref="AP14:AR14"/>
     <mergeCell ref="BH22:BJ22"/>
     <mergeCell ref="AG56:AI56"/>
+    <mergeCell ref="X73:AD73"/>
     <mergeCell ref="AJ39:AL39"/>
     <mergeCell ref="J16:P16"/>
     <mergeCell ref="BK39:BQ39"/>
@@ -18748,6 +19500,7 @@
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="Q70:W70"/>
     <mergeCell ref="AE66:AF66"/>
+    <mergeCell ref="B78:D78"/>
     <mergeCell ref="Q45:W45"/>
     <mergeCell ref="AV69:AX69"/>
     <mergeCell ref="E17:I17"/>
@@ -18805,7 +19558,9 @@
     <mergeCell ref="BE47:BG47"/>
     <mergeCell ref="AP22:AR22"/>
     <mergeCell ref="BK60:BQ60"/>
+    <mergeCell ref="AP78:AR78"/>
     <mergeCell ref="B38:D38"/>
+    <mergeCell ref="BK78:BQ78"/>
     <mergeCell ref="AJ53:AL53"/>
     <mergeCell ref="AP15:AR15"/>
     <mergeCell ref="AS16:AU16"/>
@@ -18852,7 +19607,9 @@
     <mergeCell ref="AS69:AU69"/>
     <mergeCell ref="BH56:BJ56"/>
     <mergeCell ref="X29:AD29"/>
+    <mergeCell ref="AJ73:AL73"/>
     <mergeCell ref="AP35:AR35"/>
+    <mergeCell ref="BK73:BQ73"/>
     <mergeCell ref="BH31:BJ31"/>
     <mergeCell ref="AJ48:AL48"/>
     <mergeCell ref="AV42:AX42"/>
@@ -18864,9 +19621,11 @@
     <mergeCell ref="AG70:AI70"/>
     <mergeCell ref="BB50:BD50"/>
     <mergeCell ref="X54:AD54"/>
+    <mergeCell ref="AP74:AR74"/>
     <mergeCell ref="BK20:BQ20"/>
     <mergeCell ref="AY28:BA28"/>
     <mergeCell ref="B34:D34"/>
+    <mergeCell ref="AJ77:AL77"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="AY64:BA64"/>
     <mergeCell ref="AJ68:AL68"/>
@@ -18884,6 +19643,7 @@
     <mergeCell ref="Q68:W68"/>
     <mergeCell ref="BK15:BQ15"/>
     <mergeCell ref="AE17:AF17"/>
+    <mergeCell ref="BE73:BG73"/>
     <mergeCell ref="E15:I15"/>
     <mergeCell ref="AV20:AX20"/>
     <mergeCell ref="BE48:BG48"/>
@@ -18901,6 +19661,7 @@
     <mergeCell ref="AJ46:AL46"/>
     <mergeCell ref="AJ21:AL21"/>
     <mergeCell ref="J27:P27"/>
+    <mergeCell ref="BB78:BD78"/>
     <mergeCell ref="AG25:AI25"/>
     <mergeCell ref="AY33:BA33"/>
     <mergeCell ref="A52:BQ52"/>
@@ -18912,6 +19673,7 @@
     <mergeCell ref="J20:P20"/>
     <mergeCell ref="AV47:AX47"/>
     <mergeCell ref="B43:D43"/>
+    <mergeCell ref="AY75:BA75"/>
     <mergeCell ref="BE51:BG51"/>
     <mergeCell ref="AY50:BA50"/>
     <mergeCell ref="BB55:BD55"/>
@@ -18920,8 +19682,10 @@
     <mergeCell ref="J22:P22"/>
     <mergeCell ref="BH62:BJ62"/>
     <mergeCell ref="AV38:AX38"/>
+    <mergeCell ref="X75:AD75"/>
     <mergeCell ref="N8:P8"/>
     <mergeCell ref="BK35:BQ35"/>
+    <mergeCell ref="AS77:AU77"/>
     <mergeCell ref="AY39:BA39"/>
     <mergeCell ref="AG53:AI53"/>
     <mergeCell ref="AP34:AR34"/>
@@ -18934,20 +19698,28 @@
     <mergeCell ref="BE67:BG67"/>
     <mergeCell ref="AG13:AI13"/>
     <mergeCell ref="AV33:AX33"/>
+    <mergeCell ref="AJ74:AL74"/>
     <mergeCell ref="AP36:AR36"/>
     <mergeCell ref="AS37:AU37"/>
     <mergeCell ref="AE14:AF14"/>
     <mergeCell ref="X39:AD39"/>
+    <mergeCell ref="BK74:BQ74"/>
+    <mergeCell ref="AM75:AO75"/>
     <mergeCell ref="J38:P38"/>
+    <mergeCell ref="AG78:AI78"/>
     <mergeCell ref="K7:M7"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="Q28:W28"/>
+    <mergeCell ref="AP76:AR76"/>
     <mergeCell ref="BE69:BG69"/>
     <mergeCell ref="AG15:AI15"/>
     <mergeCell ref="AJ16:AL16"/>
     <mergeCell ref="X32:AD32"/>
     <mergeCell ref="B36:D36"/>
     <mergeCell ref="E59:I59"/>
+    <mergeCell ref="AJ76:AL76"/>
+    <mergeCell ref="BK76:BQ76"/>
+    <mergeCell ref="AE78:AF78"/>
     <mergeCell ref="E46:I46"/>
     <mergeCell ref="BE62:BG62"/>
     <mergeCell ref="J15:P15"/>
@@ -18957,6 +19729,8 @@
     <mergeCell ref="AY21:BA21"/>
     <mergeCell ref="BB66:BD66"/>
     <mergeCell ref="Q67:W67"/>
+    <mergeCell ref="AG73:AI73"/>
+    <mergeCell ref="B75:D75"/>
     <mergeCell ref="AV35:AX35"/>
     <mergeCell ref="AJ11:AL11"/>
     <mergeCell ref="B31:D31"/>
@@ -18971,6 +19745,7 @@
     <mergeCell ref="X65:AD65"/>
     <mergeCell ref="AM66:AO66"/>
     <mergeCell ref="Q69:W69"/>
+    <mergeCell ref="BH75:BJ75"/>
     <mergeCell ref="AE27:AF27"/>
     <mergeCell ref="AP54:AR54"/>
     <mergeCell ref="B39:D39"/>
@@ -19005,6 +19780,7 @@
     <mergeCell ref="AJ64:AL64"/>
     <mergeCell ref="T7:V7"/>
     <mergeCell ref="J28:P28"/>
+    <mergeCell ref="AY78:BA78"/>
     <mergeCell ref="Q24:W24"/>
     <mergeCell ref="BK49:BQ49"/>
     <mergeCell ref="AG67:AI67"/>
@@ -19016,6 +19792,7 @@
     <mergeCell ref="AV41:AX41"/>
     <mergeCell ref="AE13:AF13"/>
     <mergeCell ref="AS45:AU45"/>
+    <mergeCell ref="X78:AD78"/>
     <mergeCell ref="AG69:AI69"/>
     <mergeCell ref="X53:AD53"/>
     <mergeCell ref="X47:AD47"/>
@@ -19033,6 +19810,7 @@
     <mergeCell ref="AM62:AO62"/>
     <mergeCell ref="AJ17:AL17"/>
     <mergeCell ref="AM56:AO56"/>
+    <mergeCell ref="BB74:BD74"/>
     <mergeCell ref="J54:P54"/>
     <mergeCell ref="AM43:AO43"/>
     <mergeCell ref="J41:P41"/>
@@ -19048,6 +19826,7 @@
     <mergeCell ref="X25:AD25"/>
     <mergeCell ref="BB69:BD69"/>
     <mergeCell ref="AG16:AI16"/>
+    <mergeCell ref="AY73:BA73"/>
     <mergeCell ref="E64:I64"/>
     <mergeCell ref="X71:AD71"/>
     <mergeCell ref="E51:I51"/>
@@ -19058,6 +19837,7 @@
     <mergeCell ref="BB21:BD21"/>
     <mergeCell ref="N6:P6"/>
     <mergeCell ref="AM25:AO25"/>
+    <mergeCell ref="BH78:BJ78"/>
     <mergeCell ref="E65:I65"/>
     <mergeCell ref="J59:P59"/>
     <mergeCell ref="AP32:AR32"/>
@@ -19082,16 +19862,18 @@
     <mergeCell ref="AG31:AI31"/>
     <mergeCell ref="AV56:AX56"/>
     <mergeCell ref="B58:D58"/>
+    <mergeCell ref="E75:I75"/>
     <mergeCell ref="BE60:BG60"/>
+    <mergeCell ref="AG77:AI77"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="AE13:AE17 AE19:AE25 AE27:AE29 AE31:AE39 AE41:AE43 AE45:AE51 AE53:AE56 AE58:AE60 AE62:AE71" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AE13:AE17 AE19:AE25 AE27:AE29 AE31:AE39 AE41:AE43 AE45:AE51 AE53:AE56 AE58:AE60 AE62:AE71 AE73:AE78" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N,A,B"</formula1>
     </dataValidation>
-    <dataValidation sqref="AG13:AG17 AG19:AG25 AG27:AG29 AG31:AG39 AG41:AG43 AG45:AG51 AG53:AG56 AG58:AG60 AG62:AG71" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AG13:AG17 AG19:AG25 AG27:AG29 AG31:AG39 AG41:AG43 AG45:AG51 AG53:AG56 AG58:AG60 AG62:AG71 AG73:AG78" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="AV13:AV17 AV19:AV25 AV27:AV29 AV31:AV39 AV41:AV43 AV45:AV51 AV53:AV56 AV58:AV60 AV62:AV71" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AV13:AV17 AV19:AV25 AV27:AV29 AV31:AV39 AV41:AV43 AV45:AV51 AV53:AV56 AV58:AV60 AV62:AV71 AV73:AV78" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
     <dataValidation sqref="F1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
